--- a/backend/data/Final_Users_Data.xlsx
+++ b/backend/data/Final_Users_Data.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16115" uniqueCount="8162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16115" uniqueCount="8163">
   <si>
     <t>LNDID</t>
   </si>
@@ -24513,6 +24513,9 @@
   </si>
   <si>
     <t>Surat_Simada</t>
+  </si>
+  <si>
+    <t>Junagadh</t>
   </si>
 </sst>
 </file>
@@ -68280,7 +68283,7 @@
         <v>9426960520</v>
       </c>
       <c r="F2184" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2185" spans="1:6">
@@ -68300,7 +68303,7 @@
         <v>9925498192</v>
       </c>
       <c r="F2185" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2186" spans="1:6">
@@ -68320,7 +68323,7 @@
         <v>9537227933</v>
       </c>
       <c r="F2186" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2187" spans="1:6">
@@ -68340,7 +68343,7 @@
         <v>8980565707</v>
       </c>
       <c r="F2187" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2188" spans="1:6">
@@ -68360,7 +68363,7 @@
         <v>8511166982</v>
       </c>
       <c r="F2188" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2189" spans="1:6">
@@ -68380,7 +68383,7 @@
         <v>851166982</v>
       </c>
       <c r="F2189" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2190" spans="1:6">
@@ -68400,7 +68403,7 @@
         <v>9664836295</v>
       </c>
       <c r="F2190" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2191" spans="1:6">
@@ -68420,7 +68423,7 @@
         <v>9408544315</v>
       </c>
       <c r="F2191" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2192" spans="1:6">
@@ -68440,7 +68443,7 @@
         <v>9879909892</v>
       </c>
       <c r="F2192" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2193" spans="1:6">
@@ -68460,7 +68463,7 @@
         <v>8780621177</v>
       </c>
       <c r="F2193" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2194" spans="1:6">
@@ -68480,7 +68483,7 @@
         <v>8780621177</v>
       </c>
       <c r="F2194" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2195" spans="1:6">
@@ -68500,7 +68503,7 @@
         <v>7874095336</v>
       </c>
       <c r="F2195" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2196" spans="1:6">
@@ -68520,7 +68523,7 @@
         <v>9638697699</v>
       </c>
       <c r="F2196" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2197" spans="1:6">
@@ -68540,7 +68543,7 @@
         <v>9662021405</v>
       </c>
       <c r="F2197" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2198" spans="1:6">
@@ -68560,7 +68563,7 @@
         <v>9825932408</v>
       </c>
       <c r="F2198" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2199" spans="1:6">
@@ -68580,7 +68583,7 @@
         <v>8320572025</v>
       </c>
       <c r="F2199" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2200" spans="1:6">
@@ -68600,7 +68603,7 @@
         <v>7567463376</v>
       </c>
       <c r="F2200" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2201" spans="1:6">
@@ -68620,7 +68623,7 @@
         <v>8511151265</v>
       </c>
       <c r="F2201" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2202" spans="1:6">
@@ -68640,7 +68643,7 @@
         <v>8866820255</v>
       </c>
       <c r="F2202" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2203" spans="1:6">
@@ -68660,7 +68663,7 @@
         <v>9429114097</v>
       </c>
       <c r="F2203" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2204" spans="1:6">
@@ -68680,7 +68683,7 @@
         <v>9979396733</v>
       </c>
       <c r="F2204" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2205" spans="1:6">
@@ -68700,7 +68703,7 @@
         <v>8758189914</v>
       </c>
       <c r="F2205" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2206" spans="1:6">
@@ -68720,7 +68723,7 @@
         <v>9638962193</v>
       </c>
       <c r="F2206" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2207" spans="1:6">
@@ -68740,7 +68743,7 @@
         <v>9712591191</v>
       </c>
       <c r="F2207" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2208" spans="1:6">
@@ -68760,7 +68763,7 @@
         <v>9979384966</v>
       </c>
       <c r="F2208" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2209" spans="1:6">
@@ -68780,7 +68783,7 @@
         <v>7573049465</v>
       </c>
       <c r="F2209" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2210" spans="1:6">
@@ -68800,7 +68803,7 @@
         <v>8780478678</v>
       </c>
       <c r="F2210" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2211" spans="1:6">
@@ -68820,7 +68823,7 @@
         <v>8780478678</v>
       </c>
       <c r="F2211" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2212" spans="1:6">
@@ -68840,7 +68843,7 @@
         <v>9601277246</v>
       </c>
       <c r="F2212" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2213" spans="1:6">
@@ -68860,7 +68863,7 @@
         <v>8980685969</v>
       </c>
       <c r="F2213" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2214" spans="1:6">
@@ -68880,7 +68883,7 @@
         <v>9327948210</v>
       </c>
       <c r="F2214" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2215" spans="1:6">
@@ -68900,7 +68903,7 @@
         <v>8980685969</v>
       </c>
       <c r="F2215" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2216" spans="1:6">
@@ -68920,7 +68923,7 @@
         <v>9879858126</v>
       </c>
       <c r="F2216" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2217" spans="1:6">
@@ -68940,7 +68943,7 @@
         <v>9909295942</v>
       </c>
       <c r="F2217" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2218" spans="1:6">
@@ -68960,7 +68963,7 @@
         <v>9925796997</v>
       </c>
       <c r="F2218" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2219" spans="1:6">
@@ -68980,7 +68983,7 @@
         <v>9825755249</v>
       </c>
       <c r="F2219" s="2" t="s">
-        <v>4537</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="2220" spans="1:6">
